--- a/采购合同/南通铭家纺织品有限公司采购合同-08-23.xlsx
+++ b/采购合同/南通铭家纺织品有限公司采购合同-08-23.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\欧硕\欧硕共享文件夹\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\欧硕\采购合同\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1525,7 +1525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H29"/>
@@ -1671,21 +1671,21 @@
         <v>30</v>
       </c>
       <c r="C13" s="13">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="D13" s="13">
         <v>12</v>
       </c>
       <c r="E13" s="14">
         <f>C13*D13</f>
-        <v>4860</v>
+        <v>4980</v>
       </c>
       <c r="F13" s="14">
         <v>12.3</v>
       </c>
       <c r="G13" s="14">
         <f>E13*F13</f>
-        <v>59778</v>
+        <v>61254</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>31</v>
@@ -1702,7 +1702,7 @@
       <c r="F14" s="9"/>
       <c r="G14" s="14">
         <f>SUM(G13:G13)</f>
-        <v>59778</v>
+        <v>61254</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>31</v>
